--- a/public/modelos/biblioteca-v2/PCM-MAN-004_Ordens-de-Servico_R00.xlsx
+++ b/public/modelos/biblioteca-v2/PCM-MAN-004_Ordens-de-Servico_R00.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Leia-me'!$A$1:$G$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Ordem de serviço'!$A$1:$D$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Ordens de Serviço'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Ordens de Serviço'!$A$1:$M$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Ordens de Serviço'!$A$1:$N$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cadastros'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cadastros'!$A$1:$J$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Revisões'!$1:$3</definedName>
@@ -677,6 +677,35 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color rgb="000B2A5B"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000B2A5B"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="000B2A5B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="000B2A5B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin">
         <color rgb="000B2A5B"/>
@@ -693,35 +722,6 @@
         <color rgb="000B2A5B"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="000B2A5B"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="000B2A5B"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="000B2A5B"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="000B2A5B"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -953,14 +953,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -995,8 +995,8 @@
     <xf numFmtId="2" fontId="9" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="2" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="2" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1022,8 +1022,8 @@
     <xf numFmtId="2" fontId="9" fillId="2" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="2" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1272,6 +1272,11 @@
         <t>Horas restantes. Número com vírgula (1h30 = 1,5). Vazio = sem informação; zero é valor real.</t>
       </text>
     </comment>
+    <comment ref="N3" authorId="0" shapeId="0">
+      <text>
+        <t>Observação.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1309,12 +1314,12 @@
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
-        <t>Setor.</t>
+        <t>Família de equipamento.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
-        <t>Família de equipamento.</t>
+        <t>Setor.</t>
       </text>
     </comment>
   </commentList>
@@ -1565,9 +1570,9 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tb_pcm_os" displayName="tb_pcm_os" ref="A4:M29" headerRowCount="1">
-  <autoFilter ref="A4:M29"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tb_pcm_os" displayName="tb_pcm_os" ref="A4:N29" headerRowCount="1">
+  <autoFilter ref="A4:N29"/>
+  <tableColumns count="14">
     <tableColumn id="1" name="numero_os"/>
     <tableColumn id="2" name="tag"/>
     <tableColumn id="3" name="equipamento"/>
@@ -1581,6 +1586,7 @@
     <tableColumn id="11" name="data_conclusao"/>
     <tableColumn id="12" name="horas_estimadas"/>
     <tableColumn id="13" name="horas_restantes"/>
+    <tableColumn id="14" name="observacao"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
@@ -1610,20 +1616,20 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tb_pcm_setores" displayName="tb_pcm_setores" ref="H4:H29" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tb_pcm_familias" displayName="tb_pcm_familias" ref="H4:H29" headerRowCount="1">
   <autoFilter ref="H4:H29"/>
   <tableColumns count="1">
-    <tableColumn id="8" name="nome_setor"/>
+    <tableColumn id="8" name="nome_familia"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tb_pcm_familias" displayName="tb_pcm_familias" ref="J4:J29" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tb_pcm_setores" displayName="tb_pcm_setores" ref="J4:J29" headerRowCount="1">
   <autoFilter ref="J4:J29"/>
   <tableColumns count="1">
-    <tableColumn id="10" name="nome_familia"/>
+    <tableColumn id="10" name="nome_setor"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
@@ -2504,7 +2510,7 @@
       </c>
       <c r="D19" s="33" t="inlineStr">
         <is>
-          <t>Cadastre uma vez TAG, equipamento, família e setor, as pessoas, os setores, as famílias de equipamento. Eles aparecem nas setas ▼ das outras abas.</t>
+          <t>Cadastre uma vez TAG, equipamento, família e setor, as pessoas, as famílias de equipamento, os setores. Eles aparecem nas setas ▼ das outras abas.</t>
         </is>
       </c>
       <c r="E19" s="34" t="n"/>
@@ -2538,7 +2544,7 @@
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
-          <t>Lance cada OS em uma linha e mantenha o status em dia. Prazo vencido de OS em aberto fica em vermelho.</t>
+          <t>Lance cada OS em uma linha e mantenha o status em dia. Prazo vencido de OS em aberto fica em vermelho. Use Observação, na última coluna, para anotar qualquer detalhe da OS.</t>
         </is>
       </c>
       <c r="E21" s="34" t="n"/>
@@ -3308,7 +3314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3324,6 +3330,7 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1">
@@ -3340,13 +3347,14 @@
       <c r="G1" s="84" t="n"/>
       <c r="H1" s="84" t="n"/>
       <c r="I1" s="84" t="n"/>
-      <c r="J1" s="85" t="n"/>
-      <c r="K1" s="47">
+      <c r="J1" s="84" t="n"/>
+      <c r="K1" s="84" t="n"/>
+      <c r="L1" s="85" t="n"/>
+      <c r="M1" s="47">
         <f>"Rev. "&amp;'Leia-me'!$D$15&amp;"   ·   "&amp;'Leia-me'!$D$16</f>
         <v/>
       </c>
-      <c r="L1" s="84" t="n"/>
-      <c r="M1" s="85" t="n"/>
+      <c r="N1" s="85" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="87" t="n"/>
@@ -3362,13 +3370,14 @@
       <c r="G2" s="88" t="n"/>
       <c r="H2" s="88" t="n"/>
       <c r="I2" s="88" t="n"/>
-      <c r="J2" s="89" t="n"/>
-      <c r="K2" s="51">
+      <c r="J2" s="88" t="n"/>
+      <c r="K2" s="88" t="n"/>
+      <c r="L2" s="89" t="n"/>
+      <c r="M2" s="51">
         <f>"Elaborado: "&amp;'Leia-me'!$D$13&amp;"   ·   Aprovado: "&amp;'Leia-me'!$D$14</f>
         <v/>
       </c>
-      <c r="L2" s="88" t="n"/>
-      <c r="M2" s="89" t="n"/>
+      <c r="N2" s="89" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="90" t="inlineStr">
@@ -3431,9 +3440,14 @@
           <t>Horas estimadas</t>
         </is>
       </c>
-      <c r="M3" s="92" t="inlineStr">
+      <c r="M3" s="91" t="inlineStr">
         <is>
           <t>Horas restantes</t>
+        </is>
+      </c>
+      <c r="N3" s="92" t="inlineStr">
+        <is>
+          <t>Observação</t>
         </is>
       </c>
     </row>
@@ -3501,6 +3515,11 @@
       <c r="M4" s="93" t="inlineStr">
         <is>
           <t>horas_restantes</t>
+        </is>
+      </c>
+      <c r="N4" s="93" t="inlineStr">
+        <is>
+          <t>observacao</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3539,8 @@
       <c r="J5" s="100" t="n"/>
       <c r="K5" s="100" t="n"/>
       <c r="L5" s="101" t="n"/>
-      <c r="M5" s="102" t="n"/>
+      <c r="M5" s="101" t="n"/>
+      <c r="N5" s="102" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="94" t="n"/>
@@ -3538,7 +3558,8 @@
       <c r="J6" s="100" t="n"/>
       <c r="K6" s="100" t="n"/>
       <c r="L6" s="101" t="n"/>
-      <c r="M6" s="102" t="n"/>
+      <c r="M6" s="101" t="n"/>
+      <c r="N6" s="102" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="94" t="n"/>
@@ -3556,7 +3577,8 @@
       <c r="J7" s="100" t="n"/>
       <c r="K7" s="100" t="n"/>
       <c r="L7" s="101" t="n"/>
-      <c r="M7" s="102" t="n"/>
+      <c r="M7" s="101" t="n"/>
+      <c r="N7" s="102" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="94" t="n"/>
@@ -3574,7 +3596,8 @@
       <c r="J8" s="100" t="n"/>
       <c r="K8" s="100" t="n"/>
       <c r="L8" s="101" t="n"/>
-      <c r="M8" s="102" t="n"/>
+      <c r="M8" s="101" t="n"/>
+      <c r="N8" s="102" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="94" t="n"/>
@@ -3592,7 +3615,8 @@
       <c r="J9" s="100" t="n"/>
       <c r="K9" s="100" t="n"/>
       <c r="L9" s="101" t="n"/>
-      <c r="M9" s="102" t="n"/>
+      <c r="M9" s="101" t="n"/>
+      <c r="N9" s="102" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="94" t="n"/>
@@ -3610,7 +3634,8 @@
       <c r="J10" s="100" t="n"/>
       <c r="K10" s="100" t="n"/>
       <c r="L10" s="101" t="n"/>
-      <c r="M10" s="102" t="n"/>
+      <c r="M10" s="101" t="n"/>
+      <c r="N10" s="102" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="94" t="n"/>
@@ -3628,7 +3653,8 @@
       <c r="J11" s="100" t="n"/>
       <c r="K11" s="100" t="n"/>
       <c r="L11" s="101" t="n"/>
-      <c r="M11" s="102" t="n"/>
+      <c r="M11" s="101" t="n"/>
+      <c r="N11" s="102" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="94" t="n"/>
@@ -3646,7 +3672,8 @@
       <c r="J12" s="100" t="n"/>
       <c r="K12" s="100" t="n"/>
       <c r="L12" s="101" t="n"/>
-      <c r="M12" s="102" t="n"/>
+      <c r="M12" s="101" t="n"/>
+      <c r="N12" s="102" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="94" t="n"/>
@@ -3664,7 +3691,8 @@
       <c r="J13" s="100" t="n"/>
       <c r="K13" s="100" t="n"/>
       <c r="L13" s="101" t="n"/>
-      <c r="M13" s="102" t="n"/>
+      <c r="M13" s="101" t="n"/>
+      <c r="N13" s="102" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="94" t="n"/>
@@ -3682,7 +3710,8 @@
       <c r="J14" s="100" t="n"/>
       <c r="K14" s="100" t="n"/>
       <c r="L14" s="101" t="n"/>
-      <c r="M14" s="102" t="n"/>
+      <c r="M14" s="101" t="n"/>
+      <c r="N14" s="102" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="94" t="n"/>
@@ -3700,7 +3729,8 @@
       <c r="J15" s="100" t="n"/>
       <c r="K15" s="100" t="n"/>
       <c r="L15" s="101" t="n"/>
-      <c r="M15" s="102" t="n"/>
+      <c r="M15" s="101" t="n"/>
+      <c r="N15" s="102" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="94" t="n"/>
@@ -3718,7 +3748,8 @@
       <c r="J16" s="100" t="n"/>
       <c r="K16" s="100" t="n"/>
       <c r="L16" s="101" t="n"/>
-      <c r="M16" s="102" t="n"/>
+      <c r="M16" s="101" t="n"/>
+      <c r="N16" s="102" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="94" t="n"/>
@@ -3736,7 +3767,8 @@
       <c r="J17" s="100" t="n"/>
       <c r="K17" s="100" t="n"/>
       <c r="L17" s="101" t="n"/>
-      <c r="M17" s="102" t="n"/>
+      <c r="M17" s="101" t="n"/>
+      <c r="N17" s="102" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="94" t="n"/>
@@ -3754,7 +3786,8 @@
       <c r="J18" s="100" t="n"/>
       <c r="K18" s="100" t="n"/>
       <c r="L18" s="101" t="n"/>
-      <c r="M18" s="102" t="n"/>
+      <c r="M18" s="101" t="n"/>
+      <c r="N18" s="102" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="94" t="n"/>
@@ -3772,7 +3805,8 @@
       <c r="J19" s="100" t="n"/>
       <c r="K19" s="100" t="n"/>
       <c r="L19" s="101" t="n"/>
-      <c r="M19" s="102" t="n"/>
+      <c r="M19" s="101" t="n"/>
+      <c r="N19" s="102" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="94" t="n"/>
@@ -3790,7 +3824,8 @@
       <c r="J20" s="100" t="n"/>
       <c r="K20" s="100" t="n"/>
       <c r="L20" s="101" t="n"/>
-      <c r="M20" s="102" t="n"/>
+      <c r="M20" s="101" t="n"/>
+      <c r="N20" s="102" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="94" t="n"/>
@@ -3808,7 +3843,8 @@
       <c r="J21" s="100" t="n"/>
       <c r="K21" s="100" t="n"/>
       <c r="L21" s="101" t="n"/>
-      <c r="M21" s="102" t="n"/>
+      <c r="M21" s="101" t="n"/>
+      <c r="N21" s="102" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="94" t="n"/>
@@ -3826,7 +3862,8 @@
       <c r="J22" s="100" t="n"/>
       <c r="K22" s="100" t="n"/>
       <c r="L22" s="101" t="n"/>
-      <c r="M22" s="102" t="n"/>
+      <c r="M22" s="101" t="n"/>
+      <c r="N22" s="102" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="94" t="n"/>
@@ -3844,7 +3881,8 @@
       <c r="J23" s="100" t="n"/>
       <c r="K23" s="100" t="n"/>
       <c r="L23" s="101" t="n"/>
-      <c r="M23" s="102" t="n"/>
+      <c r="M23" s="101" t="n"/>
+      <c r="N23" s="102" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="94" t="n"/>
@@ -3862,7 +3900,8 @@
       <c r="J24" s="100" t="n"/>
       <c r="K24" s="100" t="n"/>
       <c r="L24" s="101" t="n"/>
-      <c r="M24" s="102" t="n"/>
+      <c r="M24" s="101" t="n"/>
+      <c r="N24" s="102" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="94" t="n"/>
@@ -3880,7 +3919,8 @@
       <c r="J25" s="100" t="n"/>
       <c r="K25" s="100" t="n"/>
       <c r="L25" s="101" t="n"/>
-      <c r="M25" s="102" t="n"/>
+      <c r="M25" s="101" t="n"/>
+      <c r="N25" s="102" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="94" t="n"/>
@@ -3898,7 +3938,8 @@
       <c r="J26" s="100" t="n"/>
       <c r="K26" s="100" t="n"/>
       <c r="L26" s="101" t="n"/>
-      <c r="M26" s="102" t="n"/>
+      <c r="M26" s="101" t="n"/>
+      <c r="N26" s="102" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="94" t="n"/>
@@ -3916,7 +3957,8 @@
       <c r="J27" s="100" t="n"/>
       <c r="K27" s="100" t="n"/>
       <c r="L27" s="101" t="n"/>
-      <c r="M27" s="102" t="n"/>
+      <c r="M27" s="101" t="n"/>
+      <c r="N27" s="102" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="94" t="n"/>
@@ -3934,7 +3976,8 @@
       <c r="J28" s="100" t="n"/>
       <c r="K28" s="100" t="n"/>
       <c r="L28" s="101" t="n"/>
-      <c r="M28" s="102" t="n"/>
+      <c r="M28" s="101" t="n"/>
+      <c r="N28" s="102" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="103" t="n"/>
@@ -3952,7 +3995,8 @@
       <c r="J29" s="109" t="n"/>
       <c r="K29" s="109" t="n"/>
       <c r="L29" s="110" t="n"/>
-      <c r="M29" s="111" t="n"/>
+      <c r="M29" s="110" t="n"/>
+      <c r="N29" s="111" t="n"/>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="112" t="inlineStr">
@@ -4124,12 +4168,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="D2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="D1:L1"/>
     <mergeCell ref="A1:C2"/>
-    <mergeCell ref="A30:M30"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="A30:N30"/>
+    <mergeCell ref="M1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F29">
     <cfRule type="expression" priority="1" dxfId="4" stopIfTrue="1">
@@ -4241,9 +4285,9 @@
     <col width="3" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="3" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
     <col width="3" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1">
@@ -4312,12 +4356,12 @@
       </c>
       <c r="H3" s="118" t="inlineStr">
         <is>
+          <t>Família de equipamento</t>
+        </is>
+      </c>
+      <c r="J3" s="118" t="inlineStr">
+        <is>
           <t>Setor</t>
-        </is>
-      </c>
-      <c r="J3" s="118" t="inlineStr">
-        <is>
-          <t>Família de equipamento</t>
         </is>
       </c>
     </row>
@@ -4349,12 +4393,12 @@
       </c>
       <c r="H4" s="93" t="inlineStr">
         <is>
+          <t>nome_familia</t>
+        </is>
+      </c>
+      <c r="J4" s="93" t="inlineStr">
+        <is>
           <t>nome_setor</t>
-        </is>
-      </c>
-      <c r="J4" s="93" t="inlineStr">
-        <is>
-          <t>nome_familia</t>
         </is>
       </c>
     </row>
